--- a/Insurance Rate Data Scraper/output/all_states_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/all_states_final_rates.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q156"/>
+  <dimension ref="A1:Q201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13637,6 +13637,3741 @@
         </is>
       </c>
     </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>03/03/2025</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Allstate Vehicle and Property Insurance Company</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>16.600%</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>10.300%</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>9019288</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>55420</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>87565899</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>20.100%</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>4.300%</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>ALSE-134399337</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134399337/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>03/18/2025</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>18009</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>46042163</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>18.400%</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>-2.300%</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>ALSE-134450781</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134450781/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>06/23/2025</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Allstate Fire and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>201110550</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>ALSE-134490765</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134490765/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>06/30/2025</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>-3148129</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>24444</v>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>62962576</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>-4.000%</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>-11.700%</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>ALSE-134566002</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134566002/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>07/21/2025</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Allstate Insurance Company</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>19.0004 Other</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>31.000%</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>31.000%</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>65123</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>889</v>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>210221</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>77.600%</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>ALSE-134570882</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134570882/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>07/14/2025</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>-0.600%</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>-441209</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>28228</v>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>73534790</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>-1.100%</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>ALSE-134580010</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134580010/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>11/03/2025</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Allstate Insurance Company</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>18112177</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>ALSE-134650509</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134650509/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>11/03/2025</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Allstate Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>12495941</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>ALSE-134650509</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134650509/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>11/03/2025</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Allstate Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>3196373</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>ALSE-134650509</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134650509/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>10/20/2025</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Allstate Insurance Company</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>04.0001 Condominium Homeowners</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>8.800%</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>8.800%</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>205665</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>3289</v>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>2336296</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>13.700%</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>1.700%</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>ALSE-134653139</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134653139/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>10/20/2025</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Allstate Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>22.000%</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>11.400%</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>263092</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>5895</v>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>2307823</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>134.700%</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>ALSE-134662416</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134662416/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>03/26/2026</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>04.0004 Tenant Homeowners</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>19785</v>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>2482322</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>3.500%</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>-1.600%</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>ALSE-134829446</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134829446/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>04/14/2026</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>0.500%</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>414985</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>35084</v>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>82996959</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>5.000%</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>-1.000%</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>ALSE-134886800</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>Review pending</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134886800/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>06/22/2026</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Allstate Fire and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>159341552</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>ALSE-134914782</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134914782/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>04/14/2025</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Encompass Insurance Company</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>-45471</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>1423</v>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>4616938</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>7.400%</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>-5.100%</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>GMMX-134457186</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134457186/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>02/06/2025</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>GEICO Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>5.100%</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>3.200%</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>191492</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>12584</v>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>5984134</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>67.000%</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>-24.900%</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>GECC-134364417</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>2025-01-03</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134364417/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>08/18/2025</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>125</v>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>336683</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>LBPM-134578347</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134578347/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>08/18/2025</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>17836</v>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>54179090</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>LBPM-134578347</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134578347/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>12/25/2025</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>4.600%</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>1.000%</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>37</v>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>92829</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>18.000%</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>-25.000%</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>LBPM-134773946</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134773946/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>12/25/2025</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>4.600%</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>1.000%</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>485664</t>
+        </is>
+      </c>
+      <c r="I176" t="n">
+        <v>18960</v>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>48566349</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>47.000%</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>-81.000%</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>LBPM-134773946</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134773946/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>02/28/2025</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Artisan and Truckers Casualty Company</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>7.400%</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>5.700%</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>11725846</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>154310</v>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>205505042</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>136.300%</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>-28.200%</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>PRGS-134398058</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134398058/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>02/28/2025</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Progressive Universal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2.600%</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>1.300%</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>3157780</t>
+        </is>
+      </c>
+      <c r="I178" t="n">
+        <v>260080</v>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>237272763</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>35.400%</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>-28.900%</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>PRGS-134398058</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134398058/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>09/19/2025</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Artisan and Truckers Casualty Company</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>3.900%</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>4.100%</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>271254</t>
+        </is>
+      </c>
+      <c r="I179" t="n">
+        <v>5487</v>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>6615950</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>23.800%</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>-11.100%</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>PRGS-134578217</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134578217/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>09/19/2025</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Progressive Universal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>3.900%</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>3.700%</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>372679</t>
+        </is>
+      </c>
+      <c r="I180" t="n">
+        <v>9055</v>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>10072399</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>24.300%</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>-7.700%</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>PRGS-134578217</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134578217/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>10/17/2025</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Artisan and Truckers Casualty Company</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>-0.700%</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>-0.200%</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>-422660</t>
+        </is>
+      </c>
+      <c r="I181" t="n">
+        <v>159623</v>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>215211751</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>55.300%</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>-38.500%</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>PRGS-134641954</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134641954/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>10/17/2025</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Progressive Universal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>0.400%</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>-0.100%</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>-320086</t>
+        </is>
+      </c>
+      <c r="I182" t="n">
+        <v>275869</v>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>251667134</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>65.600%</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>-38.800%</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>PRGS-134641954</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134641954/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>01/16/2026</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Artisan and Truckers Casualty Company</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>-3.700%</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>-2.200%</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>-4689412</t>
+        </is>
+      </c>
+      <c r="I183" t="n">
+        <v>155154</v>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>214285533</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>3.600%</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>-8.100%</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>PRGS-134771017</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134771017/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>01/16/2026</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Progressive Universal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>-3.600%</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>-2.000%</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>-5321685</t>
+        </is>
+      </c>
+      <c r="I184" t="n">
+        <v>283800</v>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>261466362</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>3.500%</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>-12.500%</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>PRGS-134771017</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134771017/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>06/21/2025</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Oregon</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>12.300%</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>12.300%</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>411333</t>
+        </is>
+      </c>
+      <c r="I185" t="n">
+        <v>7299</v>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>3354748</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>30.400%</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>LBPM-134491645</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134491645/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>08/31/2025</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Oregon</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>-8.500%</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-2.000%</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>-3496174</t>
+        </is>
+      </c>
+      <c r="I186" t="n">
+        <v>64985</v>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>177643962</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>17.200%</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>-15.100%</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>LBPM-134586842</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134586842/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>07/20/2025</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>-8.500%</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-4.000%</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>-1100365</t>
+        </is>
+      </c>
+      <c r="I187" t="n">
+        <v>12059</v>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>27813955</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>118.500%</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>-62.800%</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>LBPM-134586929</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134586929/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>01/19/2026</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I188" t="n">
+        <v>20837</v>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>44213576</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>LBPM-134733690</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134733690/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>12/18/2025</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>-5.100%</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>-3.000%</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>-1300823</t>
+        </is>
+      </c>
+      <c r="I189" t="n">
+        <v>19230</v>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>43394746</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>9.500%</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>-17.900%</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>LBPM-134745304</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134745304/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>12/11/2025</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>-0.900%</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>-1053929</t>
+        </is>
+      </c>
+      <c r="I190" t="n">
+        <v>63473</v>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>113367175</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>-14.400%</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>LBPM-134759261</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134759261/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>05/01/2026</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Oregon</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>3.500%</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>2.500%</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>2096512</t>
+        </is>
+      </c>
+      <c r="I191" t="n">
+        <v>37092</v>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>84648203</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>2.700%</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>0.900%</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>LBPM-134824379</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134824379/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>03/15/2026</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>3.500%</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2.410%</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>2403141</t>
+        </is>
+      </c>
+      <c r="I192" t="n">
+        <v>58588</v>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>99631185</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>3.320%</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>0.210%</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>LBPM-134826073</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134826073/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>04/15/2025</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I193" t="n">
+        <v>31655</v>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>56568405</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>25.000%</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>-24.600%</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>SFMA-134294129</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134294129/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>04/15/2025</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I194" t="n">
+        <v>875163</v>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>863774489</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>60.300%</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>-37.600%</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>SFMA-134294129</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134294129/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>04/15/2025</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>04.0002 Mobile Homeowners</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>33.000%</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>32.300%</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>3828378</t>
+        </is>
+      </c>
+      <c r="I195" t="n">
+        <v>15835</v>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>11854928</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>59.600%</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>-19.300%</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>SFMA-134421427</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134421427/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>06/01/2025</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="I196" t="n">
+        <v>36387</v>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>63743659</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>SFMA-134491344</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134491344/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>06/01/2025</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="I197" t="n">
+        <v>962297</v>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>891631927</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>SFMA-134491344</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134491344/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>10/06/2025</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>-3.600%</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>-2048236</t>
+        </is>
+      </c>
+      <c r="I198" t="n">
+        <v>33690</v>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>56980415</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>SFMA-134619497</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134619497/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>10/06/2025</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>-4.200%</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>-38201187</t>
+        </is>
+      </c>
+      <c r="I199" t="n">
+        <v>985050</v>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>919545597</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>SFMA-134619497</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134619497/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>12/15/2025</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>-3.600%</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>-1839005</t>
+        </is>
+      </c>
+      <c r="I200" t="n">
+        <v>31896</v>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>50889068</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>7.700%</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>-6.800%</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>SFMA-134700697</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134700697/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>12/15/2025</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>-3.600%</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>-32649804</t>
+        </is>
+      </c>
+      <c r="I201" t="n">
+        <v>1007104</v>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>908221048</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>0.500%</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>-10.100%</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>SFMA-134700697</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134700697/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13699,7 +17434,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Idaho (ID), Washington (WA), Colorado (CO)</t>
+          <t>Idaho (ID), Washington (WA), Colorado (CO), Oregon (OR)</t>
         </is>
       </c>
     </row>
@@ -14063,7 +17798,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>ID, WA, CO only</t>
+          <t>ID, WA, CO, OR only</t>
         </is>
       </c>
     </row>
@@ -14107,7 +17842,7 @@
       <c r="A43" s="1" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Comparative analysis of approved/filed rate changes across ID/WA/CO for the named carriers</t>
+          <t>Comparative analysis of approved/filed rate changes across ID/WA/CO/OR for the named carriers</t>
         </is>
       </c>
     </row>
